--- a/Finance Policies & Procedures/Chart of Accounts/Chart of Accounts 2026-03- All.xlsx
+++ b/Finance Policies & Procedures/Chart of Accounts/Chart of Accounts 2026-03- All.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="109" documentId="13_ncr:1_{D577B4CD-8B08-4F71-8AFA-7DDFF8B97A8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D253DDBB-4E31-4216-A941-E78C5971618E}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="6630" yWindow="2430" windowWidth="6678" windowHeight="8646" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Acct Codes Description" sheetId="5" r:id="rId1"/>
@@ -1720,6 +1720,15 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1727,15 +1736,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="34" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1892,15 +1892,6 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <outline val="0"/>
@@ -1913,6 +1904,15 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1954,25 +1954,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C36F2066-8885-4F17-9D6E-333B85ADEDCE}" name="Table223" displayName="Table223" ref="A2:C41" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C36F2066-8885-4F17-9D6E-333B85ADEDCE}" name="Table223" displayName="Table223" ref="A2:C41" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{96AC4661-DD07-49DD-BBD4-831A33A9808E}" name="Account Codes" dataDxfId="20"/>
-    <tableColumn id="2" xr3:uid="{6A54D14E-3617-44DE-BC7F-B50384066142}" name="GL Titles" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{EFC45456-78CF-4BCE-9E0C-95E8AFADD946}" name="Description of the Expense" dataDxfId="18"/>
+    <tableColumn id="1" xr3:uid="{96AC4661-DD07-49DD-BBD4-831A33A9808E}" name="Account Codes" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{6A54D14E-3617-44DE-BC7F-B50384066142}" name="GL Titles" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{EFC45456-78CF-4BCE-9E0C-95E8AFADD946}" name="Description of the Expense" dataDxfId="10"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{94AF16DB-3C1E-4F28-B4CA-67085E59DEA5}" name="Table22" displayName="Table22" ref="A2:F30" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{94AF16DB-3C1E-4F28-B4CA-67085E59DEA5}" name="Table22" displayName="Table22" ref="A2:F30" totalsRowShown="0" headerRowDxfId="22" dataDxfId="21">
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{F9E87463-85DB-423E-AAE5-49B104DE72FD}" name="Account Codes" dataDxfId="15"/>
-    <tableColumn id="2" xr3:uid="{D04675A9-7C12-4DEC-8816-A4A3C6C22AD7}" name="GL Titles" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{0251BD41-5BD9-49BB-A06B-6D61E2FD7FBD}" name="Account Code " dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{0AB3B93D-B1BE-4EDE-AE20-F5FF2702C36F}" name="GL Titles  " dataDxfId="12"/>
-    <tableColumn id="7" xr3:uid="{A3B74E6A-03BD-447D-86E0-E73E9AD24A17}" name="Account Code    " dataDxfId="11"/>
-    <tableColumn id="8" xr3:uid="{B95AD356-4C4D-489B-9A0E-83EF2CA44B15}" name="GL Titles    " dataDxfId="10"/>
+    <tableColumn id="1" xr3:uid="{F9E87463-85DB-423E-AAE5-49B104DE72FD}" name="Account Codes" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{D04675A9-7C12-4DEC-8816-A4A3C6C22AD7}" name="GL Titles" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{0251BD41-5BD9-49BB-A06B-6D61E2FD7FBD}" name="Account Code " dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{0AB3B93D-B1BE-4EDE-AE20-F5FF2702C36F}" name="GL Titles  " dataDxfId="17"/>
+    <tableColumn id="7" xr3:uid="{A3B74E6A-03BD-447D-86E0-E73E9AD24A17}" name="Account Code    " dataDxfId="16"/>
+    <tableColumn id="8" xr3:uid="{B95AD356-4C4D-489B-9A0E-83EF2CA44B15}" name="GL Titles    " dataDxfId="15"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium6" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2298,11 +2298,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="10" customFormat="1" ht="21.9" x14ac:dyDescent="0.65">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="46"/>
+      <c r="B1" s="48"/>
+      <c r="C1" s="49"/>
     </row>
     <row r="2" spans="1:4" s="11" customFormat="1" ht="22.2" x14ac:dyDescent="0.35">
       <c r="A2" s="35" t="s">
@@ -2789,14 +2789,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" s="10" customFormat="1" ht="21.9" x14ac:dyDescent="0.65">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="49"/>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="46"/>
     </row>
     <row r="2" spans="1:7" s="11" customFormat="1" ht="22.5" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
@@ -4173,17 +4173,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="dc808d36-874f-4b27-aec2-2fd649817929" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f2466082-b6bf-4153-98c3-3c41e85fda18">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101003206C8355D678A459F2EF8957171B231" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a5577d833b9f28dcc6be37a04859b9a8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f2466082-b6bf-4153-98c3-3c41e85fda18" xmlns:ns3="dc808d36-874f-4b27-aec2-2fd649817929" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ae50cb7862d574a2d96b6910b4abdc85" ns2:_="" ns3:_="">
     <xsd:import namespace="f2466082-b6bf-4153-98c3-3c41e85fda18"/>
@@ -4444,6 +4433,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="dc808d36-874f-4b27-aec2-2fd649817929" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="f2466082-b6bf-4153-98c3-3c41e85fda18">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50F1AEC2-3E77-4793-ADAD-581A1EBE2C87}">
   <ds:schemaRefs>
@@ -4453,17 +4453,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3F9AB57-B337-4EA5-9E56-F7F26AFEEBD2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="dc808d36-874f-4b27-aec2-2fd649817929"/>
-    <ds:schemaRef ds:uri="f2466082-b6bf-4153-98c3-3c41e85fda18"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0E02D037-98BD-4A52-BACC-55DF958A8133}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4480,4 +4469,15 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F3F9AB57-B337-4EA5-9E56-F7F26AFEEBD2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="dc808d36-874f-4b27-aec2-2fd649817929"/>
+    <ds:schemaRef ds:uri="f2466082-b6bf-4153-98c3-3c41e85fda18"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>